--- a/assets/files/TrackDX-Import-Assistant.xlsx
+++ b/assets/files/TrackDX-Import-Assistant.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me First" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt For Claude" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Format Guide" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example — Daily" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank — Daily" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conditions Template" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procedures Template" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Med Periods Template" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Read Me First" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Prompt For Claude" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Format Guide" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Example" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Blank Template" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Example — Daily" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Blank — Daily" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Conditions Template" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Procedures Template" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Med Periods Template" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -924,6 +924,7 @@
 - Date format must be YYYY-MM-DD. Times must be HH:MM in 24-hour format.
 - Don't add columns of your own, and don't keep unmapped fields "just in case" — anything outside the layouts below is ignored on import.
 - Delete the template's example rows before handing the file back.
+- "Drinks" is the NUMBER of alcoholic drinks that day. "Drink Type" is the main drink, and it must be exactly one of these four words: Red wine, White wine, Beer, Spirits. Map whatever my data says onto one of them — vodka, whisky, gin, tequila, rum, a margarita or any other cocktail are all "Spirits"; lager, ale, IPA, stout and cider are all "Beer"; rosé, prosecco and champagne are "White wine"; name a grape and use its colour (merlot → Red wine, chardonnay → White wine). If a drink genuinely doesn't fit — sake, mead, hard seltzer, port, sherry — leave Drink Type BLANK and keep the count. Never invent a fifth value: TrackDX ignores anything outside the four, so a row saying "Margarita" imports with the count but no type and silently drops out of the drink-type breakdown. Tell me how you mapped my drinks.
 === EPISODIC LAYOUT ===
 Columns, in this order: Date, Episode Occurred, Episode Count, Triggers Logged, Trigger Start Time, Trigger End Time, Drinks, Drink Type, then a repeating group of 8 columns per episode (Episode 1 Start Time, Episode 1 End Time, Episode 1 Duration (h), Episode 1 Intensity (1-10), Episode 1 Relief Medication, Episode 1 Relief Helped, Episode 1 Suspected Cause, Episode 1 Notes — then Episode 2 …, Episode 3 …, if more than one episode ever happens on the same day).
 - "Episode Occurred" is 1 if any episode happened that day, else 0. "Episode Count" is how many.
@@ -951,6 +952,7 @@
 - Do NOT estimate or invent these. Leave them blank unless I explicitly gave you remembered numbers — TrackDX labels anything derived from them as recalled rather than recorded, and a made-up baseline would silently distort how well a procedure appears to have worked.
 "Med Periods" — which preventative medications I was on, and when. Columns: Condition, Medication, Start, End (blank End = still taking it).
 - Preventative medication history goes here, never in the daily columns.
+- IF A DOSE CHANGED, SPLIT IT INTO SEPARATE MEDICATIONS — "Depakote 500mg" and "Depakote 1000mg" — each with its own start and end, rather than one continuous period. TrackDX compares every preventative in a single model, so separate entries let it report each dose on its own; kept as one medication, a dose that worked gets averaged with one that didn't and both look mediocre. Only split when a dose lasted a month or more; ignore brief changes that were reversed. Tell me which doses you split.
 When you're done, give me the finished file as a downloadable .xlsx, and summarize the tracking mode you chose per condition, any scale conversions, and any judgment calls — so I can review before importing.</t>
         </is>
       </c>
